--- a/IPL 2025.xlsx
+++ b/IPL 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/898af4500e89e0da/Desktop/IPL Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5AC9737-2F69-4D3A-978E-B46F1184877D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A5AC9737-2F69-4D3A-978E-B46F1184877D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B56D849-9FDD-4A57-95E0-44ED3933E2A7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{67180BD0-3C86-498C-A514-907B3A9D0E8C}"/>
   </bookViews>
